--- a/data/trans_orig/IP33A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP33A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19844</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23559</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21224</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31107</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24346</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>37468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35153</t>
+          <t>35375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>30497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>49166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62288</t>
+          <t>63769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>48135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>59035</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80769</t>
+          <t>81311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60871</t>
+          <t>60771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>75585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51930</t>
+          <t>51441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68123</t>
+          <t>67436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118208</t>
+          <t>117666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140136</t>
+          <t>139942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>23351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23255</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35074</t>
+          <t>35237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,67%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>19736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30686</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25538</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44410</t>
+          <t>45034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27716</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20103</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>23855</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>30464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42033</t>
+          <t>42120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>15545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>27702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>31634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46834</t>
+          <t>47677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33760</t>
+          <t>34196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>26002</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36836</t>
+          <t>36622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51956</t>
+          <t>51113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68384</t>
+          <t>67156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>49952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>68870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52600</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89649</t>
+          <t>90814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115651</t>
+          <t>116654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66820</t>
+          <t>67066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86325</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79192</t>
+          <t>78952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96327</t>
+          <t>97076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152077</t>
+          <t>151074</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178079</t>
+          <t>176914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>56,31%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26679</t>
+          <t>26029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39621</t>
+          <t>39028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>65,5%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>33059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24225</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35165</t>
+          <t>35051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40524</t>
+          <t>40640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>55966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71949</t>
+          <t>72548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19758</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>35754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41273</t>
+          <t>41462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>53337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67872</t>
+          <t>67590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,87%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34907</t>
+          <t>34396</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>41558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>60673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43606</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31798</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43705</t>
+          <t>43875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65710</t>
+          <t>65022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83744</t>
+          <t>84137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85500</t>
+          <t>86400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60337</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82929</t>
+          <t>82457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132187</t>
+          <t>132385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163245</t>
+          <t>161853</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101979</t>
+          <t>101079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121939</t>
+          <t>122397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>110039</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132159</t>
+          <t>132506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216730</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247788</t>
+          <t>247590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41436</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>30890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47365</t>
+          <t>47802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28483</t>
+          <t>28120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40448</t>
+          <t>40902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17648</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25717</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41848</t>
+          <t>41977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49990</t>
+          <t>49536</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65435</t>
+          <t>65144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30861</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30932</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50659</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>29878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27883</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43317</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50031</t>
+          <t>48269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69758</t>
+          <t>68865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>23172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>17334</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37373</t>
+          <t>37879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36007</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23035</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33179</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50142</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>65776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60388</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98421</t>
+          <t>97439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108098</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150496</t>
+          <t>148957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82176</t>
+          <t>83013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102286</t>
+          <t>102045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98105</t>
+          <t>99087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136138</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189188</t>
+          <t>190727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231586</t>
+          <t>233861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP33A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP33A-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5741</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2997</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9277</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4911</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2214</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8245</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7762</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>38,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5741</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9263</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9610</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12354</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7788</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4454</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10485</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4937</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10526</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>61,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9610</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6088</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12552</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,6%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21583</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15351</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15351</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15351</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12699</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>12699</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>12699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15351</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>15351</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>15351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7849</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4554</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11593</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6885</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3683</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10374</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10538</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>29,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7849</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4622</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11244</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>38,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>19844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12343</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8599</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15638</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>61,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>16325</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12836</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19527</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12672</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19424</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>70,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12343</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>8948</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>15570</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>61,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>23559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33274</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20192</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20192</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20192</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>23210</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>23210</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>23210</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20192</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>20192</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>20192</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6771</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10514</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7961</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4321</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11493</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4984</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11577</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6771</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3451</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10585</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12710</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8967</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15931</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>81,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>13447</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9915</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17087</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9831</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>16424</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>79,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12710</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8896</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>16030</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>21473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31271</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19481</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19481</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19481</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>21408</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>21408</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>21408</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19481</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19481</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19075</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13596</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24574</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11387</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6707</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16500</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6622</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16038</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>27,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19075</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14055</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24968</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>42,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25477</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19978</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30956</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>30695</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25582</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35375</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>26044</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35460</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>72,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>25477</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>19584</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>30497</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>57,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49166</t>
+          <t>48601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63769</t>
+          <t>63801</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>44552</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>44552</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>44552</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>42082</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>42082</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>42082</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>44552</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>44552</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>44552</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39436</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31989</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49008</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>31145</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23815</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>38629</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24082</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>38980</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>39436</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>32140</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>48135</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59035</t>
+          <t>59979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81311</t>
+          <t>81597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>60140</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50568</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>67587</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>50,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>68255</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>60771</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>75585</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>60420</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>75318</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>60140</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>51441</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>67436</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117666</t>
+          <t>117380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139942</t>
+          <t>138998</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>99400</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>99400</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>99400</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7381</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3429</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11718</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10359</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6544</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14642</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6898</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14380</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7381</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11953</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23351</t>
+          <t>23472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18250</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13913</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22202</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11202</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6919</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15017</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7181</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14663</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>51,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18250</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13678</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22255</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23842</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25631</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25631</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25631</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21561</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>21561</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>21561</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>25631</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>25631</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>25631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9612</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5814</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>15220</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10587</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19736</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10504</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19732</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>41,8%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9612</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5941</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14008</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,48%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18471</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30789</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17482</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12990</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21280</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>21192</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16676</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25825</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16680</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25908</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>58,2%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17482</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13086</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>21153</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,52%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45034</t>
+          <t>44498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,07%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>27094</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>27094</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>27094</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>36412</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>36412</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>36412</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>27094</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>27094</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>27094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9853</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5743</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14321</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11794</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7965</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16131</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7851</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15801</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9853</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6163</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14268</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>32,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>28346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20165</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15697</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24275</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>52,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16428</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12091</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20257</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12421</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>20371</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>58,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>71,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20165</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15750</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23855</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>67,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30464</t>
+          <t>29894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42120</t>
+          <t>42823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30018</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30018</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30018</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28222</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28222</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28222</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>30018</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>30018</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30018</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17367</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12092</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23156</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21748</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15545</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27702</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16127</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27995</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>43,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17367</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12427</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23047</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,41%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31634</t>
+          <t>31041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47677</t>
+          <t>47141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31682</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25893</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36957</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>75,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>27993</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22039</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34196</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>21746</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>33614</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>56,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>31682</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>26002</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>36622</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>64,59%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>51649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67156</t>
+          <t>67749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>49741</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>49741</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>49741</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>49049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>49049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>49049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>44214</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35147</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53885</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>59122</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49952</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68870</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>49748</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>69104</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>43,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>44214</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>34716</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>52840</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90814</t>
+          <t>89882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116654</t>
+          <t>117033</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>87578</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>77907</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>96645</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>76814</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>67066</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>85984</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>66832</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>86188</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>56,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>63,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>87578</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>78952</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>97076</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151074</t>
+          <t>150695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176914</t>
+          <t>177846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,43%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>131792</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>131792</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>131792</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135936</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>135936</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>135936</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>131792</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>131792</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>131792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14660</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18701</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12052</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7527</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16986</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7563</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16912</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14660</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10064</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18831</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20554</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>33113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11806</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7765</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16330</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21064</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16130</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25589</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25553</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>48,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7635</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16402</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26029</t>
+          <t>26469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39028</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26466</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26466</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26466</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>33116</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>33116</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>33116</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>26466</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>26466</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19605</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13663</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25523</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21420</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15950</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26820</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15960</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27276</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>42,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19605</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13966</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26672</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33059</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49641</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35001</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29083</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40943</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>29581</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24181</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35051</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23725</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>35041</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>58,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35001</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27934</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40640</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,1%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55966</t>
+          <t>56527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72548</t>
+          <t>72006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>54606</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54606</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>54606</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51001</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51001</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51001</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>54606</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>54606</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>54606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13715</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19388</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13743</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9602</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17853</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9242</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18150</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>35,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13715</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9066</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19476</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>34862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36813</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31140</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41266</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>72,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>81,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24820</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20710</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28961</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20413</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29321</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>64,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>75,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36813</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>31052</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>41462</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>72,86%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53337</t>
+          <t>54229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67590</t>
+          <t>68099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50528</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>50528</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>50528</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>38563</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>38563</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>38563</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>50528</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>50528</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>50528</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23111</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17280</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29229</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28169</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21498</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34396</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21653</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35443</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>43,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23111</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>17021</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29394</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41558</t>
+          <t>42574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60673</t>
+          <t>60235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37785</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31667</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43616</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>36630</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30403</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43301</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>29356</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>43146</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>56,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37785</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>31502</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>43875</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65022</t>
+          <t>65460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84137</t>
+          <t>83121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>60896</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>60896</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>60896</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>64799</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>64799</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>64799</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>60896</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>60896</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>60896</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,107 +5989,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71091</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61208</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>82567</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>75384</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>65082</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>86400</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>64356</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>85615</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>40,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>71091</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>59990</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82457</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>45,67%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>146475</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>130916</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>162798</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>34,45%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>42,84%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>146475</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>132385</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>161853</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>38,55%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -6102,107 +6102,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>121405</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>109929</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>131288</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>63,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>112095</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>101079</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>122397</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>101864</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>123123</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>59,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,91%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>121405</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>110039</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>132506</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>63,07%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>54,33%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>65,67%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>233500</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>217177</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>249059</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>57,16%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>233500</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>218122</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>247590</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>61,45%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>187479</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>187479</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>187479</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16099</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8709</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26028</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8062</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32329</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13238</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>36433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15714</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5785</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23104</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16605</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13190</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18876</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19696</t>
+          <t>17533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>31813</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31813</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>31813</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21252</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>21252</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21252</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>61040</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61040</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61040</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18985</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13223</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25428</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10993</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6999</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15563</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33,5%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40902</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35205</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28762</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40967</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21822</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17252</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25816</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41977</t>
+          <t>25720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>58102</t>
+          <t>56840</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>49450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65144</t>
+          <t>63776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>54190</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54190</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>54190</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>32815</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>32815</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>32815</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57624</t>
+          <t>32105</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57624</t>
+          <t>32105</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57624</t>
+          <t>32105</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>86295</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>86295</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>86295</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>29307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22594</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40462</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31825</t>
+          <t>29522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>48131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33416</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24422</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40044</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>62,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>74,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>24078</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18298</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29878</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>71,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>60228</t>
+          <t>54860</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48269</t>
+          <t>44396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>63005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53729</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53729</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53729</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41946</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41946</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41946</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58744</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58744</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58744</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>100690</t>
+          <t>92527</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100690</t>
+          <t>92527</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100690</t>
+          <t>92527</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11284</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6825</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16354</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16534</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11200</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23172</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>25703</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37879</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24925</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19855</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29384</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>54,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>30612</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>23974</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35946</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64,93%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28185</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>36357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>58798</t>
+          <t>56214</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49636</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65776</t>
+          <t>62678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>36209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>36209</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>36209</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>47146</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>47146</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>47146</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40369</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40369</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40369</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>87515</t>
+          <t>81917</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>87515</t>
+          <t>81917</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>87515</t>
+          <t>81917</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>66682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54366</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84014</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>50041</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>41113</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>60145</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>75501</t>
+          <t>46432</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>37189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97439</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>125542</t>
+          <t>113114</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105823</t>
+          <t>98842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148957</t>
+          <t>135046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>109260</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>91928</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121576</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>62,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>93117</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>83013</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>102045</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>57,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>121025</t>
+          <t>92331</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99087</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136456</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>214142</t>
+          <t>201591</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190727</t>
+          <t>179659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233861</t>
+          <t>215863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
